--- a/CYP2B6/CYP2B6_Allele_def_rs_excluidos.xlsx
+++ b/CYP2B6/CYP2B6_Allele_def_rs_excluidos.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP2B6\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -303,7 +303,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="175" formatCode="0.000000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -384,7 +384,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1656,7 +1656,6 @@
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="V25" s="8">
-        <f>(SUM(V4:V24)+W22)*100</f>
         <v>14.076952326799999</v>
       </c>
     </row>

--- a/CYP2B6/CYP2B6_Allele_def_rs_excluidos.xlsx
+++ b/CYP2B6/CYP2B6_Allele_def_rs_excluidos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="94">
   <si>
     <t>rsID</t>
   </si>
@@ -296,6 +296,12 @@
   </si>
   <si>
     <t>https://gnomad.broadinstitute.org/variant/19-41012393-T-C?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>Corresponde al rs2516199080 (CYP2B6_allele_definition_table)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dbSNP, genomAD, UCSC </t>
   </si>
 </sst>
 </file>
@@ -330,7 +336,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,8 +361,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -364,28 +382,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1122,15 +1164,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="20" max="20" width="16" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="18.5703125" customWidth="1"/>
+    <col min="21" max="22" width="13.42578125" style="4" customWidth="1"/>
+    <col min="23" max="23" width="18.5703125" customWidth="1"/>
+    <col min="24" max="24" width="18.5703125" style="2" customWidth="1"/>
+    <col min="25" max="25" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,41 +1217,50 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="R1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3" t="s">
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="5"/>
+      <c r="Y1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Z1" s="5" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="T2" s="7"/>
+      <c r="U2" s="8"/>
+      <c r="V2" s="8"/>
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="7"/>
+      <c r="Z2" s="7"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1262,330 +1315,399 @@
       <c r="R3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="T3" s="7"/>
+      <c r="U3" s="8"/>
+      <c r="V3" s="8"/>
+      <c r="W3" s="7"/>
+      <c r="X3" s="7"/>
+      <c r="Y3" s="7"/>
+      <c r="Z3" s="7"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
       <c r="R4" t="s">
         <v>24</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="T4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="U4" s="7"/>
-      <c r="V4">
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="7">
         <v>0.11547839</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="7"/>
+      <c r="Y4" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z4" s="7"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="R5" t="s">
         <v>24</v>
       </c>
-      <c r="T5" s="7" t="s">
+      <c r="T5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="U5" s="7"/>
-      <c r="V5" s="2">
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="7">
         <v>2.4807691999999999E-2</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z5" s="7"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>39</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="T6" s="7" t="s">
+      <c r="T6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="U6" s="7"/>
-      <c r="V6" s="2">
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="7">
         <v>0</v>
       </c>
-      <c r="W6" s="2" t="s">
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z6" s="7"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
       <c r="Q7" t="s">
         <v>24</v>
       </c>
-      <c r="T7" s="6" t="s">
+      <c r="T7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U7" s="6"/>
-      <c r="V7" s="2"/>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U7" s="14"/>
+      <c r="V7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="W7" s="16"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z7" s="7"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>51</v>
       </c>
       <c r="S8" t="s">
         <v>52</v>
       </c>
-      <c r="T8" s="6" t="s">
+      <c r="T8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="6"/>
-      <c r="V8" s="2"/>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
       <c r="S9" t="s">
         <v>54</v>
       </c>
-      <c r="T9" s="6" t="s">
+      <c r="T9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="U9" s="6"/>
-      <c r="V9" s="2"/>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>55</v>
       </c>
       <c r="G10" t="s">
         <v>21</v>
       </c>
-      <c r="T10" s="7" t="s">
+      <c r="T10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="U10" s="7"/>
-      <c r="V10" s="2">
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="7">
         <v>7.472868E-6</v>
       </c>
-      <c r="W10" s="2" t="s">
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z10" s="7"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>56</v>
       </c>
       <c r="M11" t="s">
         <v>21</v>
       </c>
-      <c r="T11" s="7" t="s">
+      <c r="T11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="U11" s="7"/>
-      <c r="V11" s="2">
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="7">
         <v>0</v>
       </c>
-      <c r="W11" s="2" t="s">
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Z11" s="7"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
       <c r="R12" t="s">
         <v>21</v>
       </c>
-      <c r="T12" t="s">
+      <c r="T12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="V12" s="9">
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="11">
         <v>8.4769999999999995E-7</v>
       </c>
-      <c r="W12" s="2" t="s">
+      <c r="X12" s="11"/>
+      <c r="Y12" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X12" t="s">
+      <c r="Z12" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>58</v>
       </c>
       <c r="R13" t="s">
         <v>21</v>
       </c>
-      <c r="T13" t="s">
+      <c r="T13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="V13" s="9">
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="11">
         <v>8.4769999999999995E-7</v>
       </c>
-      <c r="W13" s="2" t="s">
+      <c r="X13" s="11"/>
+      <c r="Y13" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X13" s="2" t="s">
+      <c r="Z13" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>59</v>
       </c>
       <c r="F14" t="s">
         <v>23</v>
       </c>
-      <c r="T14" t="s">
+      <c r="T14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="V14">
+      <c r="U14" s="8"/>
+      <c r="V14" s="8"/>
+      <c r="W14" s="7">
         <v>7.5430000000000001E-5</v>
       </c>
-      <c r="W14" s="2" t="s">
+      <c r="X14" s="7"/>
+      <c r="Y14" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X14" t="s">
+      <c r="Z14" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>63</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
       </c>
-      <c r="T15" t="s">
+      <c r="T15" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="V15">
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="7">
         <v>1.3560000000000001E-5</v>
       </c>
-      <c r="W15" s="2" t="s">
+      <c r="X15" s="7"/>
+      <c r="Y15" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X15" t="s">
+      <c r="Z15" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>64</v>
       </c>
       <c r="J16" t="s">
         <v>21</v>
       </c>
-      <c r="T16" t="s">
+      <c r="T16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="V16">
+      <c r="U16" s="8"/>
+      <c r="V16" s="8"/>
+      <c r="W16" s="7">
         <v>3.1100000000000002E-4</v>
       </c>
-      <c r="W16" s="2" t="s">
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X16" t="s">
+      <c r="Z16" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>65</v>
       </c>
       <c r="K17" t="s">
         <v>23</v>
       </c>
-      <c r="T17" t="s">
+      <c r="T17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="V17" s="2">
+      <c r="U17" s="8"/>
+      <c r="V17" s="8"/>
+      <c r="W17" s="7">
         <v>0</v>
       </c>
-      <c r="W17" s="2" t="s">
+      <c r="X17" s="7"/>
+      <c r="Y17" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X17" t="s">
+      <c r="Z17" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>66</v>
       </c>
       <c r="O18" t="s">
         <v>21</v>
       </c>
-      <c r="T18" t="s">
+      <c r="T18" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="V18">
+      <c r="U18" s="8"/>
+      <c r="V18" s="8"/>
+      <c r="W18" s="7">
         <v>1.6949999999999999E-5</v>
       </c>
-      <c r="W18" s="2" t="s">
+      <c r="X18" s="7"/>
+      <c r="Y18" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X18" t="s">
+      <c r="Z18" s="7" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>67</v>
       </c>
       <c r="P19" t="s">
         <v>21</v>
       </c>
-      <c r="T19" t="s">
+      <c r="T19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="V19" s="2">
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="7">
         <v>0</v>
       </c>
-      <c r="W19" s="2" t="s">
+      <c r="X19" s="7"/>
+      <c r="Y19" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X19" t="s">
+      <c r="Z19" s="7" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>68</v>
       </c>
       <c r="C20" t="s">
         <v>21</v>
       </c>
-      <c r="T20" t="s">
+      <c r="T20" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="V20">
+      <c r="U20" s="8"/>
+      <c r="V20" s="8"/>
+      <c r="W20" s="7">
         <v>1.6650000000000002E-5</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="X20" s="7"/>
+      <c r="Y20" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X20" s="4" t="s">
+      <c r="Z20" s="12" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>70</v>
       </c>
       <c r="E21" t="s">
         <v>23</v>
       </c>
-      <c r="T21" s="6" t="s">
+      <c r="T21" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="U21" s="6"/>
-      <c r="V21" s="2"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="U21" s="8"/>
+      <c r="V21" s="8"/>
+      <c r="W21" s="7"/>
+      <c r="X21" s="7"/>
+      <c r="Y21" s="7"/>
+      <c r="Z21" s="7"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>71</v>
       </c>
@@ -1595,74 +1717,91 @@
       <c r="I22" t="s">
         <v>22</v>
       </c>
-      <c r="T22" t="s">
+      <c r="T22" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="U22" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="V22">
+      <c r="V22" s="8"/>
+      <c r="W22" s="7">
         <v>9.3230000000000004E-6</v>
       </c>
-      <c r="W22">
+      <c r="X22" s="7">
         <v>1.4409999999999999E-5</v>
       </c>
-      <c r="X22" t="s">
+      <c r="Y22" s="7">
+        <f>X22*W22</f>
+        <v>1.3434443000000001E-10</v>
+      </c>
+      <c r="Z22" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="AA22" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>72</v>
       </c>
       <c r="L23" t="s">
         <v>21</v>
       </c>
-      <c r="T23" t="s">
+      <c r="T23" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="V23">
+      <c r="U23" s="8"/>
+      <c r="V23" s="8"/>
+      <c r="W23" s="7">
         <v>3.3900000000000002E-6</v>
       </c>
-      <c r="W23" s="2" t="s">
+      <c r="X23" s="7"/>
+      <c r="Y23" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="Z23" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>73</v>
       </c>
       <c r="N24" t="s">
         <v>21</v>
       </c>
-      <c r="T24" t="s">
+      <c r="T24" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="V24">
+      <c r="U24" s="8"/>
+      <c r="V24" s="8"/>
+      <c r="W24" s="7">
         <v>1.3560000000000001E-5</v>
       </c>
-      <c r="W24" s="2" t="s">
+      <c r="X24" s="7"/>
+      <c r="Y24" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="X24" t="s">
+      <c r="Z24" s="7" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="V25" s="8">
-        <v>14.076952326799999</v>
-      </c>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="T25" s="7"/>
+      <c r="U25" s="8"/>
+      <c r="V25" s="8"/>
+      <c r="W25" s="13">
+        <v>14.074579040234442</v>
+      </c>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="7"/>
+      <c r="Z25" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="X20" r:id="rId1"/>
-    <hyperlink ref="X23" r:id="rId2"/>
+    <hyperlink ref="Z20" r:id="rId1"/>
+    <hyperlink ref="Z23" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CYP2B6/CYP2B6_Allele_def_rs_excluidos.xlsx
+++ b/CYP2B6/CYP2B6_Allele_def_rs_excluidos.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23010" windowHeight="9015" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="97">
   <si>
     <t>rsID</t>
   </si>
@@ -301,7 +301,16 @@
     <t>Corresponde al rs2516199080 (CYP2B6_allele_definition_table)</t>
   </si>
   <si>
-    <t xml:space="preserve">dbSNP, genomAD, UCSC </t>
+    <t>https://www.clinpgx.org/haplotype/PA165818811</t>
+  </si>
+  <si>
+    <t>CYP2B6_frequency_table</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA165818813</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166117272</t>
   </si>
 </sst>
 </file>
@@ -336,7 +345,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -364,12 +373,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,7 +405,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -425,9 +428,7 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1342,7 +1343,9 @@
       <c r="Y4" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="Z4" s="7"/>
+      <c r="Z4" s="7" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -1363,7 +1366,9 @@
       <c r="Y5" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="Z5" s="7"/>
+      <c r="Z5" s="7" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -1384,7 +1389,9 @@
       <c r="Y6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="Z6" s="7"/>
+      <c r="Z6" s="7" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -1396,16 +1403,22 @@
       <c r="T7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U7" s="14"/>
-      <c r="V7" s="15" t="s">
+      <c r="U7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="V7" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="W7" s="16"/>
+      <c r="W7" s="8">
+        <v>0</v>
+      </c>
       <c r="X7" s="7"/>
       <c r="Y7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z7" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="Z7" s="7"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -1417,12 +1430,20 @@
       <c r="T8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="U8" s="8"/>
+      <c r="U8" s="9" t="s">
+        <v>51</v>
+      </c>
       <c r="V8" s="8"/>
-      <c r="W8" s="7"/>
+      <c r="W8" s="7">
+        <v>0</v>
+      </c>
       <c r="X8" s="7"/>
-      <c r="Y8" s="7"/>
-      <c r="Z8" s="7"/>
+      <c r="Y8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z8" s="7" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -1434,12 +1455,20 @@
       <c r="T9" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="U9" s="8"/>
+      <c r="U9" s="9" t="s">
+        <v>53</v>
+      </c>
       <c r="V9" s="8"/>
-      <c r="W9" s="7"/>
+      <c r="W9" s="7">
+        <v>0</v>
+      </c>
       <c r="X9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
+      <c r="Y9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z9" s="7" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -1460,7 +1489,9 @@
       <c r="Y10" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="Z10" s="7"/>
+      <c r="Z10" s="7" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -1481,7 +1512,9 @@
       <c r="Y11" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="Z11" s="7"/>
+      <c r="Z11" s="7" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" t="s">

--- a/CYP2B6/CYP2B6_Allele_def_rs_excluidos.xlsx
+++ b/CYP2B6/CYP2B6_Allele_def_rs_excluidos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="101">
   <si>
     <t>rsID</t>
   </si>
@@ -304,13 +304,25 @@
     <t>https://www.clinpgx.org/haplotype/PA165818811</t>
   </si>
   <si>
-    <t>CYP2B6_frequency_table</t>
-  </si>
-  <si>
     <t>https://www.clinpgx.org/haplotype/PA165818813</t>
   </si>
   <si>
     <t>https://www.clinpgx.org/haplotype/PA166117272</t>
+  </si>
+  <si>
+    <t>dbSNP</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs193922917</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs193922918</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs33980385</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs3211371</t>
   </si>
 </sst>
 </file>
@@ -405,7 +417,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -429,6 +441,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1331,20 +1344,20 @@
       <c r="R4" t="s">
         <v>24</v>
       </c>
-      <c r="T4" s="9" t="s">
-        <v>28</v>
+      <c r="T4" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="U4" s="8"/>
       <c r="V4" s="8"/>
-      <c r="W4" s="7">
-        <v>0.11547839</v>
+      <c r="W4">
+        <v>9.9989999999999996E-2</v>
       </c>
       <c r="X4" s="7"/>
       <c r="Y4" s="7" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
@@ -1354,20 +1367,20 @@
       <c r="R5" t="s">
         <v>24</v>
       </c>
-      <c r="T5" s="9" t="s">
-        <v>30</v>
+      <c r="T5" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="U5" s="8"/>
       <c r="V5" s="8"/>
-      <c r="W5" s="7">
-        <v>2.4807691999999999E-2</v>
+      <c r="W5">
+        <v>9.9989999999999996E-2</v>
       </c>
       <c r="X5" s="7"/>
       <c r="Y5" s="7" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
@@ -1377,20 +1390,20 @@
       <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="T6" s="9" t="s">
-        <v>39</v>
+      <c r="T6" s="1" t="s">
+        <v>1</v>
       </c>
       <c r="U6" s="8"/>
       <c r="V6" s="8"/>
-      <c r="W6" s="7">
-        <v>0</v>
+      <c r="W6">
+        <v>6.9999999999999994E-5</v>
       </c>
       <c r="X6" s="7"/>
       <c r="Y6" s="7" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
@@ -1442,7 +1455,7 @@
         <v>79</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
@@ -1467,7 +1480,7 @@
         <v>79</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
@@ -1477,20 +1490,20 @@
       <c r="G10" t="s">
         <v>21</v>
       </c>
-      <c r="T10" s="9" t="s">
-        <v>55</v>
+      <c r="T10" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="U10" s="8"/>
       <c r="V10" s="8"/>
       <c r="W10" s="7">
-        <v>7.472868E-6</v>
+        <v>0</v>
       </c>
       <c r="X10" s="7"/>
       <c r="Y10" s="7" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
@@ -1500,8 +1513,8 @@
       <c r="M11" t="s">
         <v>21</v>
       </c>
-      <c r="T11" s="9" t="s">
-        <v>56</v>
+      <c r="T11" s="15" t="s">
+        <v>12</v>
       </c>
       <c r="U11" s="8"/>
       <c r="V11" s="8"/>
@@ -1510,10 +1523,10 @@
       </c>
       <c r="X11" s="7"/>
       <c r="Y11" s="7" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
@@ -1825,7 +1838,7 @@
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
       <c r="W25" s="13">
-        <v>14.074579040234442</v>
+        <v>20.05115584</v>
       </c>
       <c r="X25" s="13"/>
       <c r="Y25" s="7"/>
